--- a/ICT_MASTER.xlsx
+++ b/ICT_MASTER.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7695" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="History" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Replacements" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Ink" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Audit Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Replacements" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ink" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Corbel"/>
       <charset val="134"/>
@@ -34,8 +35,13 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +51,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F2937"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,10 +71,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -396,7 +411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O423"/>
+  <dimension ref="A1:P423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="1" min="1" max="2"/>
@@ -490,6 +505,11 @@
           <t>Remarks</t>
         </is>
       </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Transfer History</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16263,7 +16283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1" s="1">
@@ -16338,7 +16358,38 @@
       <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-30 05:35:19</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>restock</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16351,7 +16402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1" s="1">
@@ -16398,6 +16449,54 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-30 05:35:19</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INK</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ink restock: 1x Black (BK)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ICT Manager</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" s="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ICT_MASTER.xlsx
+++ b/ICT_MASTER.xlsx
@@ -16283,7 +16283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1" s="1">
@@ -16358,38 +16358,6 @@
       <c r="G2" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-30 05:35:19</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BK</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>restock</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16402,7 +16370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1" s="1">
@@ -16444,28 +16412,6 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>ICT Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-30 05:35:19</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>INK</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ink restock: 1x Black (BK)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
         <is>
           <t>ICT Manager</t>
         </is>

--- a/ICT_MASTER.xlsx
+++ b/ICT_MASTER.xlsx
@@ -16370,7 +16370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1" s="1">
@@ -16412,6 +16412,116 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>ICT Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-03 22:40:41</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>REPORT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PDF report generated: ICT_Report_20260603_224040.pdf</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ICT Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-03 22:47:55</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>REPORT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PDF report generated: ICT_Report_20260603_224754.pdf</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ICT Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-04 04:41:47</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>REPORT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PDF report generated: ICT_Report_20260604_044146.pdf</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ICT Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:48:35</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>REPORT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PDF report generated: ICT_Report_20260604_074835.pdf</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ICT Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:49:17</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>REPORT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PDF report generated: ICT_Report_20260604_074917.pdf</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>ICT Manager</t>
         </is>
